--- a/uk-mrtm-app-web/src/assets/files/Port_calls_and_emission_details_template_v1.xlsx
+++ b/uk-mrtm-app-web/src/assets/files/Port_calls_and_emission_details_template_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thenrbgroup-my.sharepoint.com/personal/p70860_nrb_be/Documents/Desktop/METS-Maritime/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{1EA55082-A201-437A-A93C-D6468D8C53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16577E9A-92C9-407A-BA76-76CB0208E3FF}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{1EA55082-A201-437A-A93C-D6468D8C53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D46246F-CEA2-4788-A03C-45B17B7BA7D4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2010" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F1678AC5-1FDC-45EC-A59E-DBB093098B74}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{F1678AC5-1FDC-45EC-A59E-DBB093098B74}"/>
   </bookViews>
   <sheets>
     <sheet name="Versioning" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>IMO Number</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Actual time of arrival (ATA)</t>
   </si>
   <si>
-    <t>Are you claiming a small island ferry operator surrender reduction?</t>
-  </si>
-  <si>
     <t>Fuel type</t>
   </si>
   <si>
@@ -64,12 +61,6 @@
   </si>
   <si>
     <t>Measuring unit</t>
-  </si>
-  <si>
-    <t>Carbon capture and storage (CCS) (t)</t>
-  </si>
-  <si>
-    <t>Carbon capture and utilisation (CCU) (t)</t>
   </si>
   <si>
     <t>Other fuel (O)</t>
@@ -296,6 +287,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -626,24 +621,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2" s="9">
         <v>45758</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1169,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{960C7374-8B26-41A7-A87A-39CE4911B864}">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
@@ -1177,28 +1172,23 @@
     <col min="4" max="5" width="17.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.21875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="26.21875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25.88671875" style="1" customWidth="1"/>
-    <col min="14" max="15" width="25.5546875" style="1" customWidth="1"/>
-    <col min="16" max="17" width="20.21875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="25.6640625" style="1" customWidth="1"/>
-    <col min="19" max="21" width="20.21875" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="10" width="21.44140625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="25.5546875" style="1" customWidth="1"/>
+    <col min="13" max="14" width="20.21875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="25.6640625" style="1" customWidth="1"/>
+    <col min="16" max="18" width="20.21875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
@@ -1213,50 +1203,41 @@
         <v>2</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="Q1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>14</v>
-      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="NNGXjlhpkPxbTwFkKqSI64i4V7hWJTxVbwdEAAjIAjJrMannIEcIHAVzNrZeYGsKdFzokfFYbeR87CPdc0BsNQ==" saltValue="NfTpDPQqpoi87tt44nzYKA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="IVhyzOLnQbZtG8S5GtAFSzOpU3HDXfYJEMz4VELRdEd88bVAHLSwtT1fAU2R6TGIjJdJdsKWVfaxNrClhA6kxQ==" saltValue="dAh/yKgnRypOdSzUzWMYWw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/uk-mrtm-app-web/src/assets/files/Port_calls_and_emission_details_template_v1.xlsx
+++ b/uk-mrtm-app-web/src/assets/files/Port_calls_and_emission_details_template_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thenrbgroup-my.sharepoint.com/personal/p70860_nrb_be/Documents/Desktop/METS-Maritime/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{1EA55082-A201-437A-A93C-D6468D8C53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D46246F-CEA2-4788-A03C-45B17B7BA7D4}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{1EA55082-A201-437A-A93C-D6468D8C53AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16577E9A-92C9-407A-BA76-76CB0208E3FF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{F1678AC5-1FDC-45EC-A59E-DBB093098B74}"/>
+    <workbookView xWindow="28680" yWindow="-2010" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F1678AC5-1FDC-45EC-A59E-DBB093098B74}"/>
   </bookViews>
   <sheets>
     <sheet name="Versioning" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>IMO Number</t>
   </si>
@@ -54,6 +54,9 @@
     <t>Actual time of arrival (ATA)</t>
   </si>
   <si>
+    <t>Are you claiming a small island ferry operator surrender reduction?</t>
+  </si>
+  <si>
     <t>Fuel type</t>
   </si>
   <si>
@@ -61,6 +64,12 @@
   </si>
   <si>
     <t>Measuring unit</t>
+  </si>
+  <si>
+    <t>Carbon capture and storage (CCS) (t)</t>
+  </si>
+  <si>
+    <t>Carbon capture and utilisation (CCU) (t)</t>
   </si>
   <si>
     <t>Other fuel (O)</t>
@@ -287,10 +296,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -621,24 +626,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" s="9">
         <v>45758</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1164,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{960C7374-8B26-41A7-A87A-39CE4911B864}">
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" customWidth="1"/>
@@ -1172,23 +1177,28 @@
     <col min="4" max="5" width="17.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.33203125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="21.44140625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="25.5546875" style="1" customWidth="1"/>
-    <col min="13" max="14" width="20.21875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="25.6640625" style="1" customWidth="1"/>
-    <col min="16" max="18" width="20.21875" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="20.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="30.21875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="26.21875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25.88671875" style="1" customWidth="1"/>
+    <col min="14" max="15" width="25.5546875" style="1" customWidth="1"/>
+    <col min="16" max="17" width="20.21875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="25.6640625" style="1" customWidth="1"/>
+    <col min="19" max="21" width="20.21875" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
@@ -1203,41 +1213,50 @@
         <v>2</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="O1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>11</v>
+      <c r="R1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="IVhyzOLnQbZtG8S5GtAFSzOpU3HDXfYJEMz4VELRdEd88bVAHLSwtT1fAU2R6TGIjJdJdsKWVfaxNrClhA6kxQ==" saltValue="dAh/yKgnRypOdSzUzWMYWw==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NNGXjlhpkPxbTwFkKqSI64i4V7hWJTxVbwdEAAjIAjJrMannIEcIHAVzNrZeYGsKdFzokfFYbeR87CPdc0BsNQ==" saltValue="NfTpDPQqpoi87tt44nzYKA==" spinCount="100000" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
